--- a/LISTAS/mi/BANQUETA ESCALERA Y TAPIZADA DISMAY.xlsx
+++ b/LISTAS/mi/BANQUETA ESCALERA Y TAPIZADA DISMAY.xlsx
@@ -903,14 +903,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="27" t="n">
-        <v>45163.60816182838</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="17">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -962,16 +958,6 @@
       <c r="C12" s="41" t="n"/>
       <c r="D12" s="41" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23">
       <c r="C23" s="19" t="n"/>
     </row>
@@ -1026,10 +1012,8 @@
         </is>
       </c>
       <c r="C29" s="42" t="n"/>
-      <c r="D29" s="44" t="inlineStr">
-        <is>
-          <t>********************</t>
-        </is>
+      <c r="D29" s="44" t="n">
+        <v>8979.147999999999</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="17">
@@ -1045,7 +1029,7 @@
       </c>
       <c r="C30" s="42" t="n"/>
       <c r="D30" s="44" t="n">
-        <v>2931.25</v>
+        <v>3077.813</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="17">
@@ -1065,8 +1049,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
     <row r="35" ht="18" customHeight="1" s="17">
       <c r="A35" s="29" t="n"/>
       <c r="B35" s="29" t="n"/>
@@ -1079,34 +1061,29 @@
     </row>
     <row r="37" ht="16.5" customHeight="1" s="17"/>
     <row r="38" ht="16.5" customHeight="1" s="17"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="17">
       <c r="A42" s="7" t="n"/>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="5" t="n"/>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A12:D12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/BANQUETA ESCALERA Y TAPIZADA DISMAY.xlsx
+++ b/LISTAS/mi/BANQUETA ESCALERA Y TAPIZADA DISMAY.xlsx
@@ -1072,18 +1072,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/BANQUETA ESCALERA Y TAPIZADA DISMAY.xlsx
+++ b/LISTAS/mi/BANQUETA ESCALERA Y TAPIZADA DISMAY.xlsx
@@ -903,7 +903,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="27" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -1072,18 +1072,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="A32:D32"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/BANQUETA ESCALERA Y TAPIZADA DISMAY.xlsx
+++ b/LISTAS/mi/BANQUETA ESCALERA Y TAPIZADA DISMAY.xlsx
@@ -903,7 +903,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="27" t="n">
-        <v>45254</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -1072,18 +1072,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="A32:D32"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/BANQUETA ESCALERA Y TAPIZADA DISMAY.xlsx
+++ b/LISTAS/mi/BANQUETA ESCALERA Y TAPIZADA DISMAY.xlsx
@@ -903,7 +903,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="27" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/mi/BANQUETA ESCALERA Y TAPIZADA DISMAY.xlsx
+++ b/LISTAS/mi/BANQUETA ESCALERA Y TAPIZADA DISMAY.xlsx
@@ -903,10 +903,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="27" t="n">
-        <v>45266</v>
+        <v>45264.64766263525</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="17">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -958,6 +962,16 @@
       <c r="C12" s="41" t="n"/>
       <c r="D12" s="41" t="n"/>
     </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
     <row r="23">
       <c r="C23" s="19" t="n"/>
     </row>
@@ -1012,8 +1026,10 @@
         </is>
       </c>
       <c r="C29" s="42" t="n"/>
-      <c r="D29" s="44" t="n">
-        <v>8979.147999999999</v>
+      <c r="D29" s="44" t="inlineStr">
+        <is>
+          <t>********************</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="17">
@@ -1029,7 +1045,7 @@
       </c>
       <c r="C30" s="42" t="n"/>
       <c r="D30" s="44" t="n">
-        <v>3077.813</v>
+        <v>4778.3</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="17">
@@ -1049,6 +1065,8 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
+    <row r="34"/>
     <row r="35" ht="18" customHeight="1" s="17">
       <c r="A35" s="29" t="n"/>
       <c r="B35" s="29" t="n"/>
@@ -1061,29 +1079,34 @@
     </row>
     <row r="37" ht="16.5" customHeight="1" s="17"/>
     <row r="38" ht="16.5" customHeight="1" s="17"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="17">
       <c r="A42" s="7" t="n"/>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="5" t="n"/>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A32:D32"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B29:C29"/>
     <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/BANQUETA ESCALERA Y TAPIZADA DISMAY.xlsx
+++ b/LISTAS/mi/BANQUETA ESCALERA Y TAPIZADA DISMAY.xlsx
@@ -903,14 +903,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="27" t="n">
-        <v>45264.64766263525</v>
+        <v>45272</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="17">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -962,16 +958,6 @@
       <c r="C12" s="41" t="n"/>
       <c r="D12" s="41" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23">
       <c r="C23" s="19" t="n"/>
     </row>
@@ -1045,7 +1031,7 @@
       </c>
       <c r="C30" s="42" t="n"/>
       <c r="D30" s="44" t="n">
-        <v>4778.3</v>
+        <v>11266.96</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="17">
@@ -1065,8 +1051,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
     <row r="35" ht="18" customHeight="1" s="17">
       <c r="A35" s="29" t="n"/>
       <c r="B35" s="29" t="n"/>
@@ -1079,34 +1063,29 @@
     </row>
     <row r="37" ht="16.5" customHeight="1" s="17"/>
     <row r="38" ht="16.5" customHeight="1" s="17"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="17">
       <c r="A42" s="7" t="n"/>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="5" t="n"/>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A12:D12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/BANQUETA ESCALERA Y TAPIZADA DISMAY.xlsx
+++ b/LISTAS/mi/BANQUETA ESCALERA Y TAPIZADA DISMAY.xlsx
@@ -903,7 +903,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="27" t="n">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C30" s="42" t="n"/>
       <c r="D30" s="44" t="n">
-        <v>11266.96</v>
+        <v>19960.12</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="17">

--- a/LISTAS/mi/BANQUETA ESCALERA Y TAPIZADA DISMAY.xlsx
+++ b/LISTAS/mi/BANQUETA ESCALERA Y TAPIZADA DISMAY.xlsx
@@ -903,7 +903,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="27" t="n">
-        <v>45273</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -1014,7 +1014,7 @@
       <c r="C29" s="42" t="n"/>
       <c r="D29" s="44" t="inlineStr">
         <is>
-          <t>********************</t>
+          <t>********</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C30" s="42" t="n"/>
       <c r="D30" s="44" t="n">
-        <v>19960.12</v>
+        <v>3077.813</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="17">
@@ -1074,18 +1074,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/BANQUETA ESCALERA Y TAPIZADA DISMAY.xlsx
+++ b/LISTAS/mi/BANQUETA ESCALERA Y TAPIZADA DISMAY.xlsx
@@ -903,7 +903,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="27" t="n">
-        <v>45286</v>
+        <v>45287</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -1074,18 +1074,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="A32:D32"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/BANQUETA ESCALERA Y TAPIZADA DISMAY.xlsx
+++ b/LISTAS/mi/BANQUETA ESCALERA Y TAPIZADA DISMAY.xlsx
@@ -1074,18 +1074,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/BANQUETA ESCALERA Y TAPIZADA DISMAY.xlsx
+++ b/LISTAS/mi/BANQUETA ESCALERA Y TAPIZADA DISMAY.xlsx
@@ -903,7 +903,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="27" t="n">
-        <v>45287</v>
+        <v>45288</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
